--- a/tests/fixtures/libros-template.xlsx
+++ b/tests/fixtures/libros-template.xlsx
@@ -19,22 +19,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
-    <t>Autor</t>
-  </si>
-  <si>
-    <t>Titulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N° de inventario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre del Socio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N° de Socio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha del prestamo</t>
+    <t xml:space="preserve">Nombre del Socio - 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N° de Socio - 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha del prestamo - 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autor - 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titulo - 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N° de inventario - 6</t>
   </si>
   <si>
     <t xml:space="preserve">Alejandro Dolina</t>
@@ -43,15 +43,15 @@
     <t xml:space="preserve">Bar del Infierno</t>
   </si>
   <si>
+    <t>Prueba,Julia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jorge Luis Borges</t>
   </si>
   <si>
     <t>Ficciones</t>
   </si>
   <si>
-    <t>Prueba,Julia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alejandra Pizarnik</t>
   </si>
   <si>
@@ -106,6 +106,9 @@
     <t xml:space="preserve">Reptiles y anfibios</t>
   </si>
   <si>
+    <t>Prueba,Oscar</t>
+  </si>
+  <si>
     <t>Shakspeare</t>
   </si>
   <si>
@@ -113,9 +116,6 @@
   </si>
   <si>
     <t>SN-c912f226-3432-4e37-b787-c0aaef428b1c</t>
-  </si>
-  <si>
-    <t>Prueba,Oscar</t>
   </si>
   <si>
     <t xml:space="preserve">Aquel dia en el bosque</t>
@@ -732,12 +732,15 @@
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="28"/>
-    <col customWidth="1" min="2" max="2" width="38"/>
+    <col customWidth="1" min="1" max="1" width="22.140625"/>
+    <col customWidth="1" min="2" max="2" width="17.140625"/>
     <col customWidth="1" min="3" max="3" width="23.28125"/>
-    <col customWidth="1" min="4" max="4" width="21.00390625"/>
-    <col customWidth="1" min="5" max="5" width="19.421875"/>
-    <col customWidth="1" min="6" max="6" width="25.00390625"/>
+    <col customWidth="1" min="4" max="4" width="28"/>
+    <col customWidth="1" min="5" max="5" width="38"/>
+    <col customWidth="1" min="6" max="6" width="23.28125"/>
+    <col customWidth="1" min="7" max="7" width="21.00390625"/>
+    <col customWidth="1" min="8" max="8" width="19.421875"/>
+    <col customWidth="1" min="9" max="9" width="25.00390625"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -761,13 +764,13 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2">
+      <c r="F2" s="2">
         <v>1</v>
       </c>
     </row>
@@ -775,123 +778,123 @@
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3">
         <v>9</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
+        <v>46154</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="D11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="4">
         <v>10</v>
       </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3" s="3">
-        <v>46154</v>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="s">
+    </row>
+    <row r="12" ht="14.25">
+      <c r="E12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="2">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="B12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="2">
-        <v>11</v>
-      </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="B13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C13">
+      <c r="F13">
         <v>12</v>
       </c>
     </row>
@@ -899,41 +902,41 @@
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="2">
+        <v>14</v>
+      </c>
+      <c r="C14" s="3">
+        <v>46156</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="E14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="F14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="2">
+    </row>
+    <row r="15" ht="28.5">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="2">
         <v>14</v>
       </c>
-      <c r="F14" s="3">
-        <v>46156</v>
-      </c>
-    </row>
-    <row r="15" ht="28.5">
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="3">
+        <v>46157</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="2">
-        <v>14</v>
-      </c>
-      <c r="F15" s="3">
-        <v>46157</v>
-      </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="C16" s="6"/>
+      <c r="F16" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
